--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104538_W9.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104538_W9.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.4135</v>
+        <v>8.1731</v>
       </c>
       <c r="E2" t="n">
-        <v>5.9632</v>
+        <v>6.2187</v>
       </c>
       <c r="F2" t="n">
-        <v>1.4502</v>
+        <v>1.9544</v>
       </c>
       <c r="G2" t="n">
-        <v>5.1256</v>
+        <v>5.1243</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0131</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>5.1125</v>
+        <v>5.1155</v>
       </c>
       <c r="J2" t="n">
-        <v>4.1145</v>
+        <v>4.0866</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.662</v>
+        <v>-0.6797</v>
       </c>
       <c r="L2" t="n">
-        <v>4.7765</v>
+        <v>4.7663</v>
       </c>
       <c r="M2" t="n">
-        <v>1.0111</v>
+        <v>1.0377</v>
       </c>
       <c r="N2" t="n">
-        <v>0.6751</v>
+        <v>0.6886</v>
       </c>
       <c r="O2" t="n">
-        <v>0.336</v>
+        <v>0.3492</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R2" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.6971000000000001</v>
+        <v>0.0779</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1875</v>
+        <v>0.1204</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5096000000000001</v>
+        <v>-0.0425</v>
       </c>
       <c r="V2" t="n">
-        <v>3.4387</v>
+        <v>3.4262</v>
       </c>
       <c r="W2" t="n">
-        <v>4.5314</v>
+        <v>4.5157</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="3">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.9467</v>
+        <v>7.5987</v>
       </c>
       <c r="E3" t="n">
-        <v>4.2356</v>
+        <v>5.3216</v>
       </c>
       <c r="F3" t="n">
-        <v>2.711</v>
+        <v>2.2772</v>
       </c>
       <c r="G3" t="n">
-        <v>1.2377</v>
+        <v>1.2349</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.4097</v>
+        <v>-0.4188</v>
       </c>
       <c r="I3" t="n">
-        <v>1.6473</v>
+        <v>1.6538</v>
       </c>
       <c r="J3" t="n">
-        <v>1.362</v>
+        <v>1.3288</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.9116</v>
+        <v>-0.9350000000000001</v>
       </c>
       <c r="L3" t="n">
-        <v>2.2736</v>
+        <v>2.2638</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.1243</v>
+        <v>-0.09379999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>0.5019</v>
+        <v>0.5162</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.6263</v>
+        <v>-0.61</v>
       </c>
       <c r="P3" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="R3" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.2495</v>
+        <v>0.4125</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.0434</v>
+        <v>0.0902</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7939000000000001</v>
+        <v>0.3223</v>
       </c>
       <c r="V3" t="n">
-        <v>4.3707</v>
+        <v>4.3579</v>
       </c>
       <c r="W3" t="n">
-        <v>4.3707</v>
+        <v>4.3579</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>T. HLINASON</t>
+          <t>M. KRAMPELJ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.5616</v>
+        <v>3.3954</v>
       </c>
       <c r="E4" t="n">
-        <v>1.3248</v>
+        <v>1.6134</v>
       </c>
       <c r="F4" t="n">
-        <v>2.2368</v>
+        <v>1.7821</v>
       </c>
       <c r="G4" t="n">
-        <v>2.0901</v>
+        <v>1.1001</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1255</v>
+        <v>0.5595</v>
       </c>
       <c r="I4" t="n">
-        <v>1.9646</v>
+        <v>0.5406</v>
       </c>
       <c r="J4" t="n">
-        <v>1.2095</v>
+        <v>1.5836</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4258</v>
+        <v>0.8618</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7837</v>
+        <v>0.7217</v>
       </c>
       <c r="M4" t="n">
-        <v>0.8806</v>
+        <v>-0.4835</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.3003</v>
+        <v>-0.3023</v>
       </c>
       <c r="O4" t="n">
-        <v>1.1809</v>
+        <v>-0.1811</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.1342</v>
+        <v>1.3658</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.4952</v>
+        <v>-1.1382</v>
       </c>
       <c r="R4" t="n">
-        <v>1.361</v>
+        <v>2.5039</v>
       </c>
       <c r="S4" t="n">
-        <v>3.1521</v>
+        <v>0.7003</v>
       </c>
       <c r="T4" t="n">
-        <v>2.4498</v>
+        <v>0.0785</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7023</v>
+        <v>0.6218</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.5463</v>
+        <v>0.2292</v>
       </c>
       <c r="W4" t="n">
-        <v>0.1607</v>
+        <v>1.0895</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.7071</v>
+        <v>-0.8603</v>
       </c>
     </row>
     <row r="5">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.439</v>
+        <v>3.1267</v>
       </c>
       <c r="E5" t="n">
-        <v>1.8278</v>
+        <v>1.4665</v>
       </c>
       <c r="F5" t="n">
-        <v>1.6112</v>
+        <v>1.6602</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0027</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5757</v>
+        <v>0.5772</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5731000000000001</v>
+        <v>-0.5688</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0848</v>
+        <v>0.07770000000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0102</v>
+        <v>0.0033</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.0822</v>
+        <v>-0.0694</v>
       </c>
       <c r="N5" t="n">
-        <v>0.5655</v>
+        <v>0.574</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.6477000000000001</v>
+        <v>-0.6433</v>
       </c>
       <c r="P5" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R5" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S5" t="n">
-        <v>0.7558</v>
+        <v>0.4354</v>
       </c>
       <c r="T5" t="n">
-        <v>0.8771</v>
+        <v>0.5269</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1213</v>
+        <v>-0.0915</v>
       </c>
       <c r="V5" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W5" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. KRAMPELJ</t>
+          <t>T. HLINASON</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.9923</v>
+        <v>1.9357</v>
       </c>
       <c r="E6" t="n">
-        <v>1.0968</v>
+        <v>-0.2743</v>
       </c>
       <c r="F6" t="n">
-        <v>1.8954</v>
+        <v>2.21</v>
       </c>
       <c r="G6" t="n">
-        <v>1.0933</v>
+        <v>2.1063</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5496</v>
+        <v>0.129</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5437</v>
+        <v>1.9773</v>
       </c>
       <c r="J6" t="n">
-        <v>1.6041</v>
+        <v>1.1989</v>
       </c>
       <c r="K6" t="n">
-        <v>0.8658</v>
+        <v>0.4169</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7382</v>
+        <v>0.782</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.5107</v>
+        <v>0.9074</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.3162</v>
+        <v>-0.2879</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.1945</v>
+        <v>1.1953</v>
       </c>
       <c r="P6" t="n">
-        <v>1.361</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1342</v>
+        <v>-2.5039</v>
       </c>
       <c r="R6" t="n">
-        <v>2.4952</v>
+        <v>1.3658</v>
       </c>
       <c r="S6" t="n">
-        <v>0.313</v>
+        <v>1.5123</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4657</v>
+        <v>0.873</v>
       </c>
       <c r="U6" t="n">
-        <v>0.7788</v>
+        <v>0.6393</v>
       </c>
       <c r="V6" t="n">
-        <v>0.2249</v>
+        <v>-0.5447</v>
       </c>
       <c r="W6" t="n">
-        <v>1.0927</v>
+        <v>0.1578</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.8678</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="7">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0697</v>
+        <v>1.2286</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.6419</v>
+        <v>-0.6657999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>1.7116</v>
+        <v>1.8944</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.5015</v>
+        <v>-1.5053</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.8457</v>
+        <v>-0.839</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.6558</v>
+        <v>-0.6663</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.5289</v>
+        <v>-1.5506</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.7344000000000001</v>
+        <v>-0.7379</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.7945</v>
+        <v>-0.8126</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0274</v>
+        <v>0.0452</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1113</v>
+        <v>-0.1011</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1387</v>
+        <v>0.1463</v>
       </c>
       <c r="P7" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6639</v>
+        <v>0.8234</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0212</v>
+        <v>0.0229</v>
       </c>
       <c r="U7" t="n">
-        <v>0.6427</v>
+        <v>0.8005</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="W7" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="8">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.4617</v>
+        <v>-0.0944</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.4093</v>
+        <v>-1.0602</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9476</v>
+        <v>0.9658</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.0182</v>
+        <v>-0.0073</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.4474</v>
+        <v>-0.4426</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4292</v>
+        <v>0.4352</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.6078</v>
+        <v>-0.6117</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.6825</v>
+        <v>-0.6862</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M8" t="n">
-        <v>0.5896</v>
+        <v>0.6044</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2351</v>
+        <v>0.2437</v>
       </c>
       <c r="O8" t="n">
-        <v>0.3546</v>
+        <v>0.3608</v>
       </c>
       <c r="P8" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="R8" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.124</v>
+        <v>0.2301</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3478</v>
+        <v>0.0068</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2238</v>
+        <v>0.2232</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="9">
@@ -1111,40 +1111,40 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.0655</v>
+        <v>-0.8474</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.1341</v>
+        <v>-0.0162</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.9314</v>
+        <v>-0.8312</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.7621</v>
+        <v>-0.7557</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2828</v>
+        <v>0.287</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.0449</v>
+        <v>-1.0426</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.8368</v>
+        <v>-0.8300999999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>0.2828</v>
+        <v>0.287</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.1195</v>
+        <v>-1.1171</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -1156,13 +1156,13 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3033</v>
+        <v>-0.09180000000000001</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2087</v>
+        <v>-0.0907</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.09470000000000001</v>
+        <v>-0.0011</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.3201</v>
+        <v>-2.3004</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.1943</v>
+        <v>-3.1065</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8743</v>
+        <v>0.8062</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.0669</v>
+        <v>-3.0751</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1717</v>
+        <v>0.1696</v>
       </c>
       <c r="I10" t="n">
-        <v>-3.2387</v>
+        <v>-3.2446</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.1589</v>
+        <v>-2.1888</v>
       </c>
       <c r="K10" t="n">
-        <v>0.3148</v>
+        <v>0.2995</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.4737</v>
+        <v>-2.4883</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.908</v>
+        <v>-0.8863</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1431</v>
+        <v>-0.13</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.7649</v>
+        <v>-0.7563</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.722</v>
+        <v>-2.7316</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S10" t="n">
-        <v>2.242</v>
+        <v>1.2787</v>
       </c>
       <c r="T10" t="n">
-        <v>1.5939</v>
+        <v>0.7243000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>0.6481</v>
+        <v>0.5543</v>
       </c>
       <c r="V10" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W10" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.1395</v>
+        <v>-2.876</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.2282</v>
+        <v>-1.7719</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.9113</v>
+        <v>-1.1042</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0559</v>
+        <v>0.06</v>
       </c>
       <c r="H11" t="n">
-        <v>1.2207</v>
+        <v>1.2234</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.1648</v>
+        <v>-1.1633</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.8374</v>
+        <v>-0.847</v>
       </c>
       <c r="K11" t="n">
-        <v>0.6234</v>
+        <v>0.6205000000000001</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.4608</v>
+        <v>-1.4676</v>
       </c>
       <c r="M11" t="n">
-        <v>0.8932</v>
+        <v>0.9071</v>
       </c>
       <c r="N11" t="n">
-        <v>0.5973000000000001</v>
+        <v>0.6028</v>
       </c>
       <c r="O11" t="n">
-        <v>0.2959</v>
+        <v>0.3043</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R11" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2368</v>
+        <v>0.0152</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4174</v>
+        <v>0.0556</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1805</v>
+        <v>-0.0403</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.7317</v>
+        <v>-2.7237</v>
       </c>
       <c r="W11" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.8924</v>
+        <v>-2.8814</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-9.2075</v>
+        <v>-8.7521</v>
       </c>
       <c r="E12" t="n">
-        <v>-10.6818</v>
+        <v>-10.5061</v>
       </c>
       <c r="F12" t="n">
-        <v>1.4743</v>
+        <v>1.7541</v>
       </c>
       <c r="G12" t="n">
-        <v>-4.2813</v>
+        <v>-4.2969</v>
       </c>
       <c r="H12" t="n">
-        <v>-3.9133</v>
+        <v>-3.9119</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.368</v>
+        <v>-0.3851</v>
       </c>
       <c r="J12" t="n">
-        <v>-3.4429</v>
+        <v>-3.4803</v>
       </c>
       <c r="K12" t="n">
-        <v>-3.0935</v>
+        <v>-3.1069</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.3494</v>
+        <v>-0.3735</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.8384</v>
+        <v>-0.8166</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.8198</v>
+        <v>-0.805</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.0186</v>
+        <v>-0.0116</v>
       </c>
       <c r="P12" t="n">
-        <v>-4.9903</v>
+        <v>-5.0079</v>
       </c>
       <c r="Q12" t="n">
-        <v>-6.805</v>
+        <v>-6.8289</v>
       </c>
       <c r="R12" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0641</v>
+        <v>0.5527</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.0484</v>
+        <v>0.1901</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1125</v>
+        <v>0.3627</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.3856</v>
+        <v>-0.387</v>
       </c>
       <c r="X12" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>10.2285</v>
+        <v>10.5879</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.841400000000003</v>
+        <v>-2.780800000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>13.0697</v>
+        <v>13.369</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.02469999999999839</v>
+        <v>-0.006300000000000416</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.677</v>
+        <v>-2.6578</v>
       </c>
       <c r="I13" t="n">
-        <v>2.651999999999999</v>
+        <v>2.651699999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.1264000000000007</v>
+        <v>-0.3283</v>
       </c>
       <c r="K13" t="n">
-        <v>-3.844</v>
+        <v>-3.9437</v>
       </c>
       <c r="L13" t="n">
-        <v>3.7174</v>
+        <v>3.6153</v>
       </c>
       <c r="M13" t="n">
-        <v>0.1014999999999999</v>
+        <v>0.3221000000000001</v>
       </c>
       <c r="N13" t="n">
-        <v>1.167</v>
+        <v>1.286</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.0654</v>
+        <v>-0.9634999999999998</v>
       </c>
       <c r="P13" t="n">
-        <v>-2.2684</v>
+        <v>-2.276400000000001</v>
       </c>
       <c r="Q13" t="n">
-        <v>-18.1468</v>
+        <v>-18.2105</v>
       </c>
       <c r="R13" t="n">
-        <v>15.8784</v>
+        <v>15.9343</v>
       </c>
       <c r="S13" t="n">
-        <v>5.5802</v>
+        <v>5.9467</v>
       </c>
       <c r="T13" t="n">
-        <v>2.223100000000001</v>
+        <v>2.598</v>
       </c>
       <c r="U13" t="n">
-        <v>3.357</v>
+        <v>3.3487</v>
       </c>
       <c r="V13" t="n">
-        <v>6.941700000000001</v>
+        <v>6.923899999999999</v>
       </c>
       <c r="W13" t="n">
-        <v>13.2087</v>
+        <v>13.1602</v>
       </c>
       <c r="X13" t="n">
-        <v>-6.266999999999999</v>
+        <v>-6.2361</v>
       </c>
     </row>
     <row r="14">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.7816</v>
+        <v>2.2762</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.2463</v>
+        <v>0.32</v>
       </c>
       <c r="F14" t="n">
-        <v>2.0278</v>
+        <v>1.9563</v>
       </c>
       <c r="G14" t="n">
-        <v>3.0838</v>
+        <v>3.0887</v>
       </c>
       <c r="H14" t="n">
-        <v>1.1832</v>
+        <v>1.1833</v>
       </c>
       <c r="I14" t="n">
-        <v>1.9006</v>
+        <v>1.9054</v>
       </c>
       <c r="J14" t="n">
-        <v>2.3846</v>
+        <v>2.3697</v>
       </c>
       <c r="K14" t="n">
-        <v>1.1531</v>
+        <v>1.1409</v>
       </c>
       <c r="L14" t="n">
-        <v>1.2315</v>
+        <v>1.2288</v>
       </c>
       <c r="M14" t="n">
-        <v>0.6992</v>
+        <v>0.719</v>
       </c>
       <c r="N14" t="n">
-        <v>0.0301</v>
+        <v>0.0424</v>
       </c>
       <c r="O14" t="n">
-        <v>0.6691</v>
+        <v>0.6766</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R14" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.599</v>
+        <v>-1.1068</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.8861</v>
+        <v>-0.2954</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.7129</v>
+        <v>-0.8115</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.6105</v>
+        <v>-0.6162</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.6105</v>
+        <v>-0.6162</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.8695000000000001</v>
+        <v>0.294</v>
       </c>
       <c r="E15" t="n">
-        <v>0.5255</v>
+        <v>0.0262</v>
       </c>
       <c r="F15" t="n">
-        <v>0.344</v>
+        <v>0.2679</v>
       </c>
       <c r="G15" t="n">
-        <v>2.2622</v>
+        <v>2.2526</v>
       </c>
       <c r="H15" t="n">
-        <v>0.1084</v>
+        <v>0.0955</v>
       </c>
       <c r="I15" t="n">
-        <v>2.1538</v>
+        <v>2.1571</v>
       </c>
       <c r="J15" t="n">
-        <v>1.7262</v>
+        <v>1.7034</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.662</v>
+        <v>-0.6797</v>
       </c>
       <c r="L15" t="n">
-        <v>2.3883</v>
+        <v>2.3832</v>
       </c>
       <c r="M15" t="n">
-        <v>0.536</v>
+        <v>0.5492</v>
       </c>
       <c r="N15" t="n">
-        <v>0.7705</v>
+        <v>0.7752</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.2345</v>
+        <v>-0.226</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R15" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0765</v>
+        <v>-0.4912</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1603</v>
+        <v>-0.3115</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0838</v>
+        <v>-0.1797</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.0155</v>
+        <v>-1.0121</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.0155</v>
+        <v>-1.0121</v>
       </c>
     </row>
     <row r="16">
@@ -1657,58 +1657,58 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6098</v>
+        <v>0.1364</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.0707</v>
+        <v>-0.5465</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="G16" t="n">
-        <v>0.4343</v>
+        <v>0.4337</v>
       </c>
       <c r="H16" t="n">
-        <v>0.2771</v>
+        <v>0.2758</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="J16" t="n">
-        <v>0.2771</v>
+        <v>0.2758</v>
       </c>
       <c r="K16" t="n">
-        <v>0.2771</v>
+        <v>0.2758</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R16" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S16" t="n">
-        <v>0.6291</v>
+        <v>0.1579</v>
       </c>
       <c r="T16" t="n">
-        <v>0.7864</v>
+        <v>0.3159</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1573</v>
+        <v>-0.1579</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5353</v>
+        <v>-0.0427</v>
       </c>
       <c r="E17" t="n">
-        <v>1.9171</v>
+        <v>1.5142</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.3818</v>
+        <v>-1.5569</v>
       </c>
       <c r="G17" t="n">
-        <v>0.9812</v>
+        <v>0.9758</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1283</v>
+        <v>0.1346</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8529</v>
+        <v>0.8411</v>
       </c>
       <c r="J17" t="n">
-        <v>1.6333</v>
+        <v>1.6027</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1141</v>
+        <v>0.1067</v>
       </c>
       <c r="L17" t="n">
-        <v>1.5192</v>
+        <v>1.496</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.6521</v>
+        <v>-0.627</v>
       </c>
       <c r="N17" t="n">
-        <v>0.0142</v>
+        <v>0.028</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.6663</v>
+        <v>-0.6549</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R17" t="n">
-        <v>2.722</v>
+        <v>2.7316</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3953</v>
+        <v>-0.1778</v>
       </c>
       <c r="T17" t="n">
-        <v>0.4083</v>
+        <v>0.0575</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.013</v>
+        <v>-0.2353</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W17" t="n">
-        <v>3.278</v>
+        <v>3.2684</v>
       </c>
       <c r="X17" t="n">
-        <v>-3.4387</v>
+        <v>-3.4262</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>E. VILA</t>
+          <t>A. ALBICY</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.6201</v>
+        <v>-0.4122</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.1533</v>
+        <v>-2.67</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4668</v>
+        <v>2.2579</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.4517</v>
+        <v>-0.5979</v>
       </c>
       <c r="H18" t="n">
-        <v>0.6941000000000001</v>
+        <v>0.6373</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.1458</v>
+        <v>-1.2352</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.9613</v>
+        <v>-0.1144</v>
       </c>
       <c r="K18" t="n">
-        <v>0.5368000000000001</v>
+        <v>0.6238</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.4981</v>
+        <v>-0.7382</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.4904</v>
+        <v>-0.4835</v>
       </c>
       <c r="N18" t="n">
-        <v>0.1573</v>
+        <v>0.0135</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.6477000000000001</v>
+        <v>-0.497</v>
       </c>
       <c r="P18" t="n">
-        <v>0.4537</v>
+        <v>0.6829</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-2.2763</v>
       </c>
       <c r="R18" t="n">
-        <v>0.4537</v>
+        <v>2.9592</v>
       </c>
       <c r="S18" t="n">
-        <v>0.2172</v>
+        <v>-0.4972</v>
       </c>
       <c r="T18" t="n">
-        <v>0.6472</v>
+        <v>-0.2793</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4301</v>
+        <v>-0.2179</v>
       </c>
       <c r="V18" t="n">
-        <v>0.1607</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0.1607</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. ALBICY</t>
+          <t>I. WONG</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.6483</v>
+        <v>-0.4697</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.8717</v>
+        <v>0.4396</v>
       </c>
       <c r="F19" t="n">
-        <v>2.2234</v>
+        <v>-0.9094</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.5969</v>
+        <v>1.8294</v>
       </c>
       <c r="H19" t="n">
-        <v>0.6319</v>
+        <v>-0.3932</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.2289</v>
+        <v>2.2226</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.0862</v>
+        <v>0.7339</v>
       </c>
       <c r="K19" t="n">
-        <v>0.6336000000000001</v>
+        <v>-1.4554</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.7198</v>
+        <v>2.1893</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.5107</v>
+        <v>1.0955</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.0017</v>
+        <v>1.0622</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.509</v>
+        <v>0.0333</v>
       </c>
       <c r="P19" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.2683</v>
+        <v>-0.2276</v>
       </c>
       <c r="R19" t="n">
-        <v>2.9488</v>
+        <v>0.9105</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.7319</v>
+        <v>-1.0382</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5172</v>
+        <v>-0.7692</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2148</v>
+        <v>-0.2691</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-1.9438</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.7025</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-2.6463</v>
       </c>
     </row>
     <row r="20">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.7715</v>
+        <v>-0.6826</v>
       </c>
       <c r="E20" t="n">
-        <v>1.014</v>
+        <v>1.2423</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.7855</v>
+        <v>-1.9249</v>
       </c>
       <c r="G20" t="n">
-        <v>1.7042</v>
+        <v>1.7081</v>
       </c>
       <c r="H20" t="n">
-        <v>1.896</v>
+        <v>1.8956</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1919</v>
+        <v>-0.1875</v>
       </c>
       <c r="J20" t="n">
-        <v>1.7973</v>
+        <v>1.7907</v>
       </c>
       <c r="K20" t="n">
-        <v>1.1256</v>
+        <v>1.1204</v>
       </c>
       <c r="L20" t="n">
-        <v>0.6717</v>
+        <v>0.6703</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.0931</v>
+        <v>-0.08260000000000001</v>
       </c>
       <c r="N20" t="n">
-        <v>0.7705</v>
+        <v>0.7752</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.8636</v>
+        <v>-0.8578</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R20" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3675</v>
+        <v>-0.2892</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5565</v>
+        <v>-0.3207</v>
       </c>
       <c r="U20" t="n">
-        <v>0.189</v>
+        <v>0.0316</v>
       </c>
       <c r="V20" t="n">
-        <v>-2.1082</v>
+        <v>-2.1016</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.1082</v>
+        <v>-2.1016</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>I. WONG</t>
+          <t>E. VILA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.8374</v>
+        <v>-0.7987</v>
       </c>
       <c r="E21" t="n">
-        <v>0.3518</v>
+        <v>-0.3994</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.1892</v>
+        <v>-0.3994</v>
       </c>
       <c r="G21" t="n">
-        <v>1.8323</v>
+        <v>-1.4559</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.3881</v>
+        <v>0.6923</v>
       </c>
       <c r="I21" t="n">
-        <v>2.2204</v>
+        <v>-2.1481</v>
       </c>
       <c r="J21" t="n">
-        <v>0.7577</v>
+        <v>-0.9705</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.4413</v>
+        <v>0.5343</v>
       </c>
       <c r="L21" t="n">
-        <v>2.199</v>
+        <v>-1.5048</v>
       </c>
       <c r="M21" t="n">
-        <v>1.0746</v>
+        <v>-0.4854</v>
       </c>
       <c r="N21" t="n">
-        <v>1.0532</v>
+        <v>0.1579</v>
       </c>
       <c r="O21" t="n">
-        <v>0.0214</v>
+        <v>-0.6433</v>
       </c>
       <c r="P21" t="n">
-        <v>0.6805</v>
+        <v>0.4553</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.2268</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.9073</v>
+        <v>0.4553</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.4027</v>
+        <v>0.0441</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8861</v>
+        <v>0.4133</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5165999999999999</v>
+        <v>-0.3692</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.9475</v>
+        <v>0.1578</v>
       </c>
       <c r="W21" t="n">
-        <v>0.7071</v>
+        <v>0.1578</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.6546</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.5741</v>
+        <v>-1.7391</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.1106</v>
+        <v>-3.1457</v>
       </c>
       <c r="F22" t="n">
-        <v>1.5365</v>
+        <v>1.4067</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.5851</v>
+        <v>-1.589</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.0258</v>
+        <v>-0.034</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.5593</v>
+        <v>-1.555</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.3452</v>
+        <v>-2.3686</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.9218</v>
+        <v>-0.9383</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.4234</v>
+        <v>-1.4303</v>
       </c>
       <c r="M22" t="n">
-        <v>0.7601</v>
+        <v>0.7796</v>
       </c>
       <c r="N22" t="n">
-        <v>0.8959</v>
+        <v>0.9043</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.1359</v>
+        <v>-0.1246</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R22" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3856</v>
+        <v>-0.5446</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.0434</v>
+        <v>-1.0455</v>
       </c>
       <c r="U22" t="n">
-        <v>0.6578000000000001</v>
+        <v>0.501</v>
       </c>
       <c r="V22" t="n">
-        <v>0.6235000000000001</v>
+        <v>0.6221</v>
       </c>
       <c r="W22" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.0155</v>
+        <v>-1.0121</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.742</v>
+        <v>-2.5524</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.1515</v>
+        <v>-3.1821</v>
       </c>
       <c r="F23" t="n">
-        <v>0.4095</v>
+        <v>0.6297</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.6218</v>
+        <v>-3.6244</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.6781</v>
+        <v>-2.6768</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.9436</v>
+        <v>-0.9476</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.7138</v>
+        <v>-2.7381</v>
       </c>
       <c r="K23" t="n">
-        <v>-2.2205</v>
+        <v>-2.231</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.4932</v>
+        <v>-0.5071</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.908</v>
+        <v>-0.8863</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.4576</v>
+        <v>-0.4458</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.4504</v>
+        <v>-0.4405</v>
       </c>
       <c r="P23" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R23" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.8668</v>
+        <v>-0.6807</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3962</v>
+        <v>-0.3953</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4706</v>
+        <v>-0.2854</v>
       </c>
       <c r="V23" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
       <c r="W23" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.1452</v>
+        <v>-2.9616</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.7373</v>
+        <v>-3.6544</v>
       </c>
       <c r="F24" t="n">
-        <v>0.5921</v>
+        <v>0.6929</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.5808</v>
+        <v>-2.5876</v>
       </c>
       <c r="H24" t="n">
-        <v>0.9697</v>
+        <v>0.9653</v>
       </c>
       <c r="I24" t="n">
-        <v>-3.5505</v>
+        <v>-3.5528</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.9287</v>
+        <v>-1.9606</v>
       </c>
       <c r="K24" t="n">
-        <v>0.9555</v>
+        <v>0.9373</v>
       </c>
       <c r="L24" t="n">
-        <v>-2.8842</v>
+        <v>-2.8979</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.6521</v>
+        <v>-0.627</v>
       </c>
       <c r="N24" t="n">
-        <v>0.0142</v>
+        <v>0.028</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.6663</v>
+        <v>-0.6549</v>
       </c>
       <c r="P24" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R24" t="n">
-        <v>2.9488</v>
+        <v>2.9592</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.1257</v>
+        <v>-0.9478</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6744</v>
+        <v>-0.5557</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.4513</v>
+        <v>-0.3921</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.686</v>
+        <v>-3.2872</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.5368</v>
+        <v>-3.313</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.1492</v>
+        <v>0.0258</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.4369</v>
+        <v>-0.4274</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.1198</v>
+        <v>-0.1179</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.3171</v>
+        <v>-0.3095</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.6425</v>
+        <v>-0.6462</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.7171</v>
+        <v>-0.7207</v>
       </c>
       <c r="L25" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M25" t="n">
-        <v>0.2055</v>
+        <v>0.2189</v>
       </c>
       <c r="N25" t="n">
-        <v>0.5973000000000001</v>
+        <v>0.6028</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.3918</v>
+        <v>-0.384</v>
       </c>
       <c r="P25" t="n">
-        <v>-1.8147</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q25" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R25" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.4189</v>
+        <v>-0.0267</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.3992</v>
+        <v>-0.1628</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.0197</v>
+        <v>0.1361</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.0155</v>
+        <v>-1.0121</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.0155</v>
+        <v>-1.0121</v>
       </c>
     </row>
     <row r="26">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-10.2284</v>
+        <v>-10.2396</v>
       </c>
       <c r="E26" t="n">
-        <v>-13.0698</v>
+        <v>-13.3688</v>
       </c>
       <c r="F26" t="n">
-        <v>2.841299999999999</v>
+        <v>3.129499999999999</v>
       </c>
       <c r="G26" t="n">
-        <v>0.02479999999999999</v>
+        <v>0.006099999999999994</v>
       </c>
       <c r="H26" t="n">
-        <v>2.676899999999999</v>
+        <v>2.6578</v>
       </c>
       <c r="I26" t="n">
-        <v>-2.652099999999999</v>
+        <v>-2.6516</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.1015000000000014</v>
+        <v>-0.3222000000000006</v>
       </c>
       <c r="K26" t="n">
-        <v>-1.1669</v>
+        <v>-1.285899999999999</v>
       </c>
       <c r="L26" t="n">
-        <v>1.065600000000001</v>
+        <v>0.9638000000000009</v>
       </c>
       <c r="M26" t="n">
-        <v>0.1263000000000001</v>
+        <v>0.3282999999999998</v>
       </c>
       <c r="N26" t="n">
-        <v>3.843900000000001</v>
+        <v>3.9437</v>
       </c>
       <c r="O26" t="n">
-        <v>-3.7177</v>
+        <v>-3.6152</v>
       </c>
       <c r="P26" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="Q26" t="n">
-        <v>-15.8784</v>
+        <v>-15.9343</v>
       </c>
       <c r="R26" t="n">
-        <v>18.1466</v>
+        <v>18.2105</v>
       </c>
       <c r="S26" t="n">
-        <v>-5.58</v>
+        <v>-5.5982</v>
       </c>
       <c r="T26" t="n">
-        <v>-3.3569</v>
+        <v>-3.3487</v>
       </c>
       <c r="U26" t="n">
-        <v>-2.2233</v>
+        <v>-2.2494</v>
       </c>
       <c r="V26" t="n">
-        <v>-6.9415</v>
+        <v>-6.923900000000001</v>
       </c>
       <c r="W26" t="n">
-        <v>6.266999999999999</v>
+        <v>6.2362</v>
       </c>
       <c r="X26" t="n">
-        <v>-13.2085</v>
+        <v>-13.1601</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104538_W9.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104538_W9.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104538_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104538_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-0.8603</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104538_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104538_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104538_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104538_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104538_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104538_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>0</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104538_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-2.8814</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104538_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104538_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-6.2361</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>0</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104538_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-1.0121</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104538_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104538_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-3.4262</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104538_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104538_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-2.6463</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104538_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-2.1016</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104538_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104538_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-1.0121</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104538_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104538_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104538_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>-1.0121</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104538_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,7 @@
       <c r="X26" t="n">
         <v>-13.1601</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
